--- a/PaintShop_Test.xlsx
+++ b/PaintShop_Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys.sharepoint.com/sites/TW-or/Gedeelde documenten/or/2026-2027/Jaar 2/OR5 - Improving Search/exam/assignment Paint Shop/Python/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8770FD2B-09BC-4196-A167-78E78C1AFA6B}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A19DA0-E144-45C9-A93E-6BFCCADDED18}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -935,20 +935,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -971,14 +971,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -986,4 +978,12 @@
     <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>